--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486548_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486548_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.341200000000001</v>
+        <v>8.328799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7734</v>
+        <v>5.7301</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5679</v>
+        <v>2.5987</v>
       </c>
       <c r="G2" t="n">
         <v>6.1583</v>
@@ -610,13 +610,13 @@
         <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5995</v>
+        <v>-0.612</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0769</v>
+        <v>-0.1202</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5226</v>
+        <v>-0.4918</v>
       </c>
       <c r="V2" t="n">
         <v>1.695</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3385</v>
+        <v>5.5101</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9315</v>
+        <v>2.5963</v>
       </c>
       <c r="F3" t="n">
-        <v>3.407</v>
+        <v>2.9138</v>
       </c>
       <c r="G3" t="n">
         <v>4.7075</v>
@@ -688,13 +688,13 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5016</v>
+        <v>-0.3269</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1286</v>
+        <v>-0.2067</v>
       </c>
       <c r="U3" t="n">
-        <v>0.373</v>
+        <v>-0.1202</v>
       </c>
       <c r="V3" t="n">
         <v>2.4345</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3549</v>
+        <v>2.3664</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4835</v>
+        <v>1.3717</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8714</v>
+        <v>0.9947</v>
       </c>
       <c r="G4" t="n">
         <v>0.7126</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0548</v>
+        <v>-0.0433</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2656</v>
+        <v>0.1538</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3204</v>
+        <v>-0.1971</v>
       </c>
       <c r="V4" t="n">
         <v>0.1745</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2203</v>
+        <v>1.9269</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0412</v>
+        <v>1.0569</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1792</v>
+        <v>0.87</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.126</v>
+        <v>1.8191</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3474</v>
+        <v>0.003</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4734</v>
+        <v>1.816</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1778</v>
+        <v>2.0399</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1013</v>
+        <v>0.2039</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0765</v>
+        <v>1.836</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3038</v>
+        <v>-0.2208</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2461</v>
+        <v>-0.2009</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5499</v>
+        <v>-0.0199</v>
       </c>
       <c r="P5" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4763</v>
+        <v>0.1078</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6682</v>
+        <v>0.1046</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8081</v>
+        <v>0.0033</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5723</v>
+        <v>1.8559</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6099</v>
+        <v>1.0459</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9625</v>
+        <v>0.8099</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8191</v>
+        <v>1.6089</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003</v>
+        <v>0.8239</v>
       </c>
       <c r="I6" t="n">
-        <v>1.816</v>
+        <v>0.7849</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0399</v>
+        <v>0.609</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2039</v>
+        <v>0.5292</v>
       </c>
       <c r="L6" t="n">
-        <v>1.836</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2208</v>
+        <v>0.9999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2009</v>
+        <v>0.2947</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0199</v>
+        <v>0.7052</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2467</v>
+        <v>-1.318</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3425</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0958</v>
+        <v>-0.5825</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1015</v>
+        <v>1.1559</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7539</v>
+        <v>1.4391</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3476</v>
+        <v>-0.2832</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6089</v>
+        <v>-0.126</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8239</v>
+        <v>1.3474</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7849</v>
+        <v>-1.4734</v>
       </c>
       <c r="J7" t="n">
-        <v>0.609</v>
+        <v>1.1778</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5292</v>
+        <v>1.1013</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0765</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9999</v>
+        <v>-1.3038</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2947</v>
+        <v>0.2461</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7052</v>
+        <v>-1.5499</v>
       </c>
       <c r="P7" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0723</v>
+        <v>0.4119</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0274</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0449</v>
+        <v>0.3458</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2599</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3127</v>
+        <v>0.6355</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8712</v>
+        <v>-1.5792</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1838</v>
+        <v>2.2147</v>
       </c>
       <c r="G8" t="n">
         <v>2.0802</v>
@@ -1078,13 +1078,13 @@
         <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1151</v>
+        <v>-0.7922</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9589</v>
+        <v>-0.6669</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1561</v>
+        <v>-0.1253</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6749</v>
+        <v>-2.1671</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4761</v>
+        <v>-3.1841</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8012</v>
+        <v>1.017</v>
       </c>
       <c r="G9" t="n">
         <v>2.0775</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4027</v>
+        <v>-0.895</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0274</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3753</v>
+        <v>-0.1595</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7395</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3736</v>
+        <v>-3.0097</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.474</v>
+        <v>-1.917</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-1.0927</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8938</v>
+        <v>-1.8163</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3375</v>
+        <v>0.5535</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5563</v>
+        <v>-2.3698</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9925</v>
+        <v>-0.797</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2857</v>
+        <v>0.7879</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7068</v>
+        <v>-1.5849</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9013</v>
+        <v>-1.0193</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0519</v>
+        <v>-0.2344</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8495</v>
+        <v>-0.7849</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0857</v>
+        <v>-0.2809</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1286</v>
+        <v>-0.0324</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0429</v>
+        <v>-0.2485</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1745</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5492</v>
+        <v>-3.6164</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.364</v>
+        <v>-2.8092</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1852</v>
+        <v>-0.8072</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8163</v>
+        <v>-1.8938</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5535</v>
+        <v>-0.3375</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3698</v>
+        <v>-1.5563</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.797</v>
+        <v>-0.9925</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7879</v>
+        <v>-0.2857</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5849</v>
+        <v>-0.7068</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0193</v>
+        <v>-0.9013</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2344</v>
+        <v>-0.0519</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7849</v>
+        <v>-0.8495</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2175</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8204</v>
+        <v>-0.1571</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4795</v>
+        <v>-0.2067</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3409</v>
+        <v>0.0496</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.13</v>
+        <v>0.1745</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.6437</v>
+        <v>12.9863</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4081</v>
+        <v>3.750499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>9.235700000000001</v>
+        <v>9.2357</v>
       </c>
       <c r="G12" t="n">
         <v>15.328</v>
@@ -1360,7 +1360,7 @@
         <v>11.6026</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7252</v>
+        <v>3.725199999999999</v>
       </c>
       <c r="J12" t="n">
         <v>14.5125</v>
@@ -1372,13 +1372,13 @@
         <v>4.123899999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8154999999999999</v>
+        <v>0.8154999999999994</v>
       </c>
       <c r="N12" t="n">
         <v>1.214</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3985999999999998</v>
+        <v>-0.3986000000000003</v>
       </c>
       <c r="P12" t="n">
         <v>-2.1752</v>
@@ -1390,10 +1390,10 @@
         <v>14.1378</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.2479</v>
+        <v>-3.9057</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.7216</v>
+        <v>-2.3792</v>
       </c>
       <c r="U12" t="n">
         <v>-1.5262</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3731</v>
+        <v>2.9955</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6856</v>
+        <v>2.4621</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6875</v>
+        <v>0.5334</v>
       </c>
       <c r="G13" t="n">
         <v>-0.006</v>
@@ -1468,13 +1468,13 @@
         <v>1.9576</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2263</v>
+        <v>0.8487</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6802</v>
+        <v>0.4567</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5462</v>
+        <v>0.392</v>
       </c>
       <c r="V13" t="n">
         <v>0.1952</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8912</v>
+        <v>1.1808</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7409</v>
+        <v>1.4638</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6321</v>
+        <v>-0.283</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.3119</v>
+        <v>0.4561</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.5214</v>
+        <v>-0.2587</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2096</v>
+        <v>0.7148</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.2757</v>
+        <v>1.289</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7601</v>
+        <v>0.6387</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5155999999999999</v>
+        <v>0.6502</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0362</v>
+        <v>-0.8328</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7613</v>
+        <v>-0.8974</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7251</v>
+        <v>0.0645</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6101</v>
+        <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6805</v>
+        <v>0.2244</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6223</v>
+        <v>-0.0204</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0582</v>
+        <v>0.2448</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7029</v>
+        <v>0.7621</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0167</v>
+        <v>-1.7467</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3138</v>
+        <v>2.5088</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4561</v>
+        <v>-2.3119</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2587</v>
+        <v>-2.5214</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7148</v>
+        <v>0.2096</v>
       </c>
       <c r="J15" t="n">
-        <v>1.289</v>
+        <v>-1.2757</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6387</v>
+        <v>-0.7601</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6502</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8328</v>
+        <v>-1.0362</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8974</v>
+        <v>-1.7613</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0645</v>
+        <v>0.7251</v>
       </c>
       <c r="P15" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>0.87</v>
+        <v>2.6101</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2534</v>
+        <v>1.5514</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4675</v>
+        <v>0.6165</v>
       </c>
       <c r="U15" t="n">
-        <v>0.214</v>
+        <v>0.9349</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4393</v>
+        <v>-0.8863</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3756</v>
+        <v>0.2215</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4867</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8358</v>
+        <v>0.2346</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4026</v>
+        <v>-0.0445</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4332</v>
+        <v>0.2791</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1818</v>
+        <v>-1.0507</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0933</v>
+        <v>-0.8698</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0885</v>
+        <v>-0.181</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8976</v>
@@ -1858,13 +1858,13 @@
         <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1542</v>
+        <v>-0.0231</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4795</v>
+        <v>-0.256</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3253</v>
+        <v>0.2328</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.364</v>
+        <v>-2.6285</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4838</v>
+        <v>-1.5243</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8478</v>
+        <v>-1.1042</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5945</v>
+        <v>-2.958</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9426</v>
+        <v>0.4231</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6519</v>
+        <v>-3.381</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4548</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6078</v>
+        <v>2.1843</v>
       </c>
       <c r="L19" t="n">
-        <v>0.153</v>
+        <v>-2.1937</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1397</v>
+        <v>-2.9486</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3348</v>
+        <v>-1.7613</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-1.1873</v>
       </c>
       <c r="P19" t="n">
-        <v>0.87</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>1.36</v>
+        <v>0.6775</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0707</v>
+        <v>0.6177</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2892</v>
+        <v>0.0598</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.9995</v>
+        <v>0.7395</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9554</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.9549</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>F. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8829</v>
+        <v>-2.7497</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7478</v>
+        <v>-1.7659</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1351</v>
+        <v>-0.9838</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.958</v>
+        <v>-1.924</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4231</v>
+        <v>-2.2444</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.381</v>
+        <v>0.3203</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.8354</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1843</v>
+        <v>-1.429</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.1937</v>
+        <v>0.5937</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.9486</v>
+        <v>-1.0887</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7613</v>
+        <v>-0.8153</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1873</v>
+        <v>-0.2733</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.0875</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q20" t="n">
         <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4231</v>
+        <v>0.1319</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3942</v>
+        <v>0.0721</v>
       </c>
       <c r="U20" t="n">
-        <v>0.029</v>
+        <v>0.0598</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7395</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3904</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LOBO MARTORELL</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4078</v>
+        <v>-2.9035</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2417</v>
+        <v>0.0368</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8339</v>
+        <v>-2.9402</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1732</v>
+        <v>-1.5945</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8273</v>
+        <v>-0.9426</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3459</v>
+        <v>-0.6519</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3339</v>
+        <v>-0.4548</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5594</v>
+        <v>-0.6078</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7746</v>
+        <v>0.153</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-1.1397</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2679</v>
+        <v>-0.3348</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5714</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2227</v>
+        <v>0.8205</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0721</v>
+        <v>0.6237</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1506</v>
+        <v>0.1968</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1952</v>
+        <v>-2.9995</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0.9554</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-3.9549</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. ZURBRIGGEN</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9212</v>
+        <v>-3.1358</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.66</v>
+        <v>-1.7598</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2612</v>
+        <v>-1.376</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.924</v>
+        <v>-0.4847</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2444</v>
+        <v>-2.5517</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3203</v>
+        <v>2.0671</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8354</v>
+        <v>1.3626</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.429</v>
+        <v>-1.1069</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5937</v>
+        <v>2.4695</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0887</v>
+        <v>-1.8473</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8153</v>
+        <v>-1.4449</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2733</v>
+        <v>-0.4024</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5225</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0396</v>
+        <v>-0.1292</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.822</v>
+        <v>-0.2079</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2176</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5649999999999999</v>
+        <v>-1.8695</v>
       </c>
       <c r="W22" t="n">
-        <v>2.2599</v>
+        <v>-0.7395</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.695</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>J. LOBO MARTORELL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9913</v>
+        <v>-3.6506</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4304</v>
+        <v>-4.577</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5609</v>
+        <v>0.9264</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4847</v>
+        <v>-3.1732</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5517</v>
+        <v>-0.8273</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0671</v>
+        <v>-2.3459</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3626</v>
+        <v>-2.3339</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1069</v>
+        <v>-0.5594</v>
       </c>
       <c r="L23" t="n">
-        <v>2.4695</v>
+        <v>-1.7746</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8473</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4449</v>
+        <v>-0.2679</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4024</v>
+        <v>-0.5714</v>
       </c>
       <c r="P23" t="n">
         <v>-0.6525</v>
@@ -2248,22 +2248,22 @@
         <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9847</v>
+        <v>-0.0201</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8784</v>
+        <v>-0.2632</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1062</v>
+        <v>0.243</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8695</v>
+        <v>0.1952</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.644</v>
+        <v>-12.6437</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.235799999999999</v>
+        <v>-9.235600000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.408200000000001</v>
+        <v>-3.4081</v>
       </c>
       <c r="G24" t="n">
         <v>-15.328</v>
@@ -2296,10 +2296,10 @@
         <v>-11.6026</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.725199999999999</v>
+        <v>-3.7252</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8153999999999999</v>
+        <v>-0.8154000000000003</v>
       </c>
       <c r="K24" t="n">
         <v>-1.2142</v>
@@ -2326,13 +2326,13 @@
         <v>16.313</v>
       </c>
       <c r="S24" t="n">
-        <v>4.247999999999999</v>
+        <v>4.248099999999999</v>
       </c>
       <c r="T24" t="n">
         <v>1.5262</v>
       </c>
       <c r="U24" t="n">
-        <v>2.7219</v>
+        <v>2.7217</v>
       </c>
       <c r="V24" t="n">
         <v>-3.7391</v>
@@ -2341,7 +2341,7 @@
         <v>4.1914</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.9305</v>
+        <v>-7.930499999999999</v>
       </c>
     </row>
   </sheetData>
